--- a/public/공동실습소 출석부.xlsx
+++ b/public/공동실습소 출석부.xlsx
@@ -20,6 +20,15 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="158">
   <si>
+    <t>2기 자동차고 2반</t>
+  </si>
+  <si>
+    <t>3기 전북인공지능고</t>
+  </si>
+  <si>
+    <t>1기 자동차고 1반</t>
+  </si>
+  <si>
     <t>번호</t>
   </si>
   <si>
@@ -29,22 +38,31 @@
     <t>월요일</t>
   </si>
   <si>
+    <t>월요일(4/6)</t>
+  </si>
+  <si>
     <t>화요일</t>
+  </si>
+  <si>
+    <t>화요일(4/7)</t>
+  </si>
+  <si>
+    <t>수요일(4/8)</t>
   </si>
   <si>
     <t>수요일</t>
   </si>
   <si>
+    <t>목요일(4/9)</t>
+  </si>
+  <si>
     <t>목요일</t>
   </si>
   <si>
-    <t>금요일</t>
+    <t>금요일(4/10)</t>
   </si>
   <si>
-    <t>2기 자동차고 2반</t>
-  </si>
-  <si>
-    <t>3기 전북인공지능고</t>
+    <t>금요일</t>
   </si>
   <si>
     <t>결과 수</t>
@@ -56,40 +74,16 @@
     <t>미이수여부</t>
   </si>
   <si>
-    <t>1기 자동차고 1반</t>
+    <t>공결</t>
   </si>
   <si>
     <t>강은재</t>
   </si>
   <si>
-    <t>월요일(4/6)</t>
-  </si>
-  <si>
-    <t>화요일(4/7)</t>
-  </si>
-  <si>
-    <t>수요일(4/8)</t>
-  </si>
-  <si>
-    <t>목요일(4/9)</t>
-  </si>
-  <si>
-    <t>금요일(4/10)</t>
-  </si>
-  <si>
     <t>카이세 수이</t>
   </si>
   <si>
-    <t>공결</t>
-  </si>
-  <si>
     <t>강성식</t>
-  </si>
-  <si>
-    <t>김경민</t>
-  </si>
-  <si>
-    <t>김도훈</t>
   </si>
   <si>
     <t>고재현</t>
@@ -98,10 +92,13 @@
     <t>공도윤(미)</t>
   </si>
   <si>
-    <t>김영준</t>
+    <t>김경민</t>
   </si>
   <si>
     <t>김태빈</t>
+  </si>
+  <si>
+    <t>김도훈</t>
   </si>
   <si>
     <t>4.7종료</t>
@@ -110,49 +107,49 @@
     <t>김민기</t>
   </si>
   <si>
+    <t>서장원</t>
+  </si>
+  <si>
+    <t>김영준</t>
+  </si>
+  <si>
+    <t>김시우</t>
+  </si>
+  <si>
     <t>김지후</t>
   </si>
   <si>
-    <t>서장원</t>
+    <t>신채원</t>
+  </si>
+  <si>
+    <t>김지안</t>
   </si>
   <si>
     <t>나종엽</t>
   </si>
   <si>
-    <t>신채원</t>
-  </si>
-  <si>
-    <t>김시우</t>
+    <t>양지훈</t>
   </si>
   <si>
     <t>노태규</t>
   </si>
   <si>
-    <t>양지훈</t>
+    <t>김태수</t>
   </si>
   <si>
-    <t>김지안</t>
+    <t>이연아</t>
   </si>
   <si>
     <t>양진영</t>
   </si>
   <si>
-    <t>이연아</t>
-  </si>
-  <si>
-    <t>김태수</t>
-  </si>
-  <si>
     <t>이하람</t>
-  </si>
-  <si>
-    <t>이성호</t>
   </si>
   <si>
     <t>변석민</t>
   </si>
   <si>
-    <t>이진현</t>
+    <t>이성호</t>
   </si>
   <si>
     <t>장현우</t>
@@ -161,7 +158,7 @@
     <t>안율</t>
   </si>
   <si>
-    <t>임지섭</t>
+    <t>이진현</t>
   </si>
   <si>
     <t>전기현</t>
@@ -170,43 +167,46 @@
     <t>유찬</t>
   </si>
   <si>
-    <t>장주원</t>
+    <t>임지섭</t>
   </si>
   <si>
     <t>조성준</t>
   </si>
   <si>
-    <t>주영일</t>
+    <t>이은성</t>
   </si>
   <si>
-    <t>이은성</t>
+    <t>장주원</t>
+  </si>
+  <si>
+    <t>이하준</t>
   </si>
   <si>
     <t>최은유</t>
   </si>
   <si>
-    <t>함예찬</t>
+    <t>주영일</t>
   </si>
   <si>
-    <t>이하준</t>
+    <t>이한결</t>
   </si>
   <si>
     <t>최한별</t>
   </si>
   <si>
-    <t>황인태</t>
+    <t>임현승</t>
   </si>
   <si>
-    <t>이한결</t>
+    <t>함예찬</t>
   </si>
   <si>
     <t>한우주</t>
   </si>
   <si>
-    <t>임현승</t>
+    <t>한율(미)</t>
   </si>
   <si>
-    <t>한율(미)</t>
+    <t>황인태</t>
   </si>
   <si>
     <t>홍준서</t>
@@ -238,28 +238,28 @@
 조성준 (질병결)</t>
   </si>
   <si>
+    <t>4번 김영준 조퇴
+8번 양진영 결석</t>
+  </si>
+  <si>
     <t>강성식, 김지안, 안율, 이은성 
 자격증시험
 공도윤, 한율 미인정결</t>
+  </si>
+  <si>
+    <t>1번 강은재, 10번 이진현 지각
+8번 양진영 결석</t>
   </si>
   <si>
     <t>한율 1교시 후 미인정 조퇴
 변석민 자격증시험</t>
   </si>
   <si>
-    <t>김민기 자격증시험</t>
-  </si>
-  <si>
-    <t>4번 김영준 조퇴
+    <t>1번 강은재, 10번 이진현 지각 &amp; 4교시 이후 미인정 조퇴
 8번 양진영 결석</t>
   </si>
   <si>
-    <t>1번 강은재, 10번 이진현 지각
-8번 양진영 결석</t>
-  </si>
-  <si>
-    <t>1번 강은재, 10번 이진현 지각 &amp; 4교시 이후 미인정 조퇴
-8번 양진영 결석</t>
+    <t>김민기 자격증시험</t>
   </si>
   <si>
     <t>1번 강은재, 10번 이진현, 8번 양진영 결석</t>
@@ -271,22 +271,19 @@
     <t>강현우</t>
   </si>
   <si>
-    <t>김동연</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>6기 기계과 5반</t>
   </si>
   <si>
-    <t>김민재</t>
-  </si>
-  <si>
     <t>금요일(7/20일 월요일)</t>
   </si>
   <si>
-    <t>김유현</t>
+    <t>7기 기계과 6반</t>
+  </si>
+  <si>
+    <t>김동연</t>
   </si>
   <si>
     <t>강동완</t>
@@ -295,194 +292,187 @@
     <t>권율</t>
   </si>
   <si>
+    <t>김민재</t>
+  </si>
+  <si>
+    <t>곽민준</t>
+  </si>
+  <si>
+    <t>김유현</t>
+  </si>
+  <si>
+    <t>김명준</t>
+  </si>
+  <si>
     <t>김주원</t>
+  </si>
+  <si>
+    <t>구성록</t>
+  </si>
+  <si>
+    <t>김상준</t>
   </si>
   <si>
     <t>김중현</t>
   </si>
   <si>
-    <t>7기 기계과 6반</t>
+    <t>김장호</t>
   </si>
   <si>
-    <t>김명준</t>
+    <t>김세헌</t>
+  </si>
+  <si>
+    <t>김민규</t>
+  </si>
+  <si>
+    <t>김현성</t>
   </si>
   <si>
     <t>박성민</t>
   </si>
   <si>
-    <t>구성록</t>
+    <t>김유빈</t>
+  </si>
+  <si>
+    <t>박정현</t>
   </si>
   <si>
     <t>박지원</t>
   </si>
   <si>
-    <t>김장호</t>
+    <t>김종수</t>
   </si>
   <si>
-    <t>곽민준</t>
-  </si>
-  <si>
-    <t>김민규</t>
+    <t>김은찬</t>
   </si>
   <si>
     <t>배성재</t>
   </si>
   <si>
-    <t>김현성</t>
+    <t>박주경</t>
   </si>
   <si>
-    <t>김종수</t>
+    <t>김태양</t>
+  </si>
+  <si>
+    <t>김일권</t>
+  </si>
+  <si>
+    <t>박주형</t>
   </si>
   <si>
     <t>손경원</t>
   </si>
   <si>
-    <t>박정현</t>
+    <t>김재민</t>
+  </si>
+  <si>
+    <t>나은호</t>
+  </si>
+  <si>
+    <t>박채빈</t>
   </si>
   <si>
     <t>심의석</t>
   </si>
   <si>
-    <t>김태양</t>
+    <t>김준서</t>
   </si>
   <si>
-    <t>김상준</t>
+    <t>박현준</t>
+  </si>
+  <si>
+    <t>서재원</t>
   </si>
   <si>
     <t>양경환</t>
   </si>
   <si>
-    <t>박주경</t>
+    <t>반위진</t>
   </si>
   <si>
-    <t>나은호</t>
-  </si>
-  <si>
-    <t>김세헌</t>
+    <t>송현우</t>
   </si>
   <si>
     <t>오종현</t>
   </si>
   <si>
-    <t>박주형</t>
-  </si>
-  <si>
-    <t>박현준</t>
-  </si>
-  <si>
-    <t>김유빈</t>
+    <t>신희재</t>
   </si>
   <si>
     <t>임지호</t>
   </si>
   <si>
-    <t>박채빈</t>
+    <t>김태호</t>
   </si>
   <si>
-    <t>반위진</t>
+    <t>선민규</t>
   </si>
   <si>
     <t>임한결</t>
   </si>
   <si>
-    <t>김은찬</t>
+    <t>양병우</t>
   </si>
   <si>
-    <t>서재원</t>
-  </si>
-  <si>
-    <t>선민규</t>
+    <t>윤서진</t>
   </si>
   <si>
     <t>전정혁</t>
   </si>
   <si>
-    <t>송현우</t>
+    <t>김현빈</t>
   </si>
   <si>
-    <t>김일권</t>
+    <t>진용호</t>
   </si>
   <si>
-    <t>양병우</t>
+    <t>이윤호</t>
   </si>
   <si>
     <t>최신원</t>
   </si>
   <si>
-    <t>신희재</t>
+    <t>문순호</t>
   </si>
   <si>
-    <t>김재민</t>
+    <t>최강현</t>
   </si>
   <si>
-    <t>진용호</t>
+    <t>임찬영</t>
   </si>
   <si>
     <t>한재희</t>
   </si>
   <si>
-    <t>윤서진</t>
+    <t>정현우</t>
   </si>
   <si>
-    <t>최강현</t>
+    <t>박소찬</t>
   </si>
   <si>
-    <t>김준서</t>
+    <t>조운휘</t>
+  </si>
+  <si>
+    <t>서동우</t>
   </si>
   <si>
     <t>최우진</t>
   </si>
   <si>
-    <t>이윤호</t>
+    <t>황연우</t>
   </si>
   <si>
-    <t>김태호</t>
-  </si>
-  <si>
-    <t>임찬영</t>
+    <t>서지후</t>
   </si>
   <si>
     <t>11번 1교시 미인정지각</t>
   </si>
   <si>
-    <t>정현우</t>
-  </si>
-  <si>
-    <t>김현빈</t>
-  </si>
-  <si>
-    <t>조운휘</t>
-  </si>
-  <si>
-    <t>문순호</t>
-  </si>
-  <si>
-    <t>황연우</t>
-  </si>
-  <si>
-    <t>박소찬</t>
+    <t>석민권</t>
   </si>
   <si>
     <t>황희훈</t>
-  </si>
-  <si>
-    <t>서동우</t>
-  </si>
-  <si>
-    <t>서지후</t>
-  </si>
-  <si>
-    <t>석민권</t>
-  </si>
-  <si>
-    <t>김종수 질병결</t>
-  </si>
-  <si>
-    <t>나은호, 박현준 미인정결,
-진용호 질병결</t>
-  </si>
-  <si>
-    <t>강동완, 김민규 질병결</t>
   </si>
   <si>
     <t>유건빈</t>
@@ -501,6 +491,16 @@
   </si>
   <si>
     <t>한재훈</t>
+  </si>
+  <si>
+    <t>김종수 질병결</t>
+  </si>
+  <si>
+    <t>나은호, 박현준 미인정결,
+진용호 질병결</t>
+  </si>
+  <si>
+    <t>강동완, 김민규 질병결</t>
   </si>
 </sst>
 </file>
@@ -595,7 +595,13 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -609,12 +615,6 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -634,11 +634,11 @@
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -665,15 +665,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -983,25 +983,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -1108,119 +1108,119 @@
         <v>6.0</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="7" t="b">
+      <c r="B4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI4" s="4">
@@ -1244,7 +1244,7 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="12" t="b">
         <v>0</v>
@@ -1363,7 +1363,7 @@
         <v>3.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" s="12" t="b">
         <v>0</v>
@@ -1482,7 +1482,7 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C7" s="12" t="b">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="17" t="b">
         <v>0</v>
@@ -1621,25 +1621,25 @@
       <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="b">
+      <c r="I8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P8" s="17" t="b">
@@ -1660,25 +1660,25 @@
       <c r="U8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="18" t="b">
+      <c r="V8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC8" s="17" t="b">
@@ -1720,7 +1720,7 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C9" s="12" t="b">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12" t="b">
         <v>0</v>
@@ -1958,7 +1958,7 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C11" s="12" t="b">
         <v>0</v>
@@ -2077,7 +2077,7 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="12" t="b">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" s="12" t="b">
         <v>0</v>
@@ -2311,106 +2311,106 @@
       <c r="AN13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>11.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="7" t="b">
+      <c r="B14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI14" s="4">
@@ -2434,7 +2434,7 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C15" s="12" t="b">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C16" s="12" t="b">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C17" s="12" t="b">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C18" s="17" t="b">
         <v>0</v>
@@ -2811,25 +2811,25 @@
       <c r="H18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="18" t="b">
+      <c r="I18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P18" s="17" t="b">
@@ -2850,25 +2850,25 @@
       <c r="U18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="18" t="b">
+      <c r="V18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC18" s="17" t="b">
@@ -3279,25 +3279,25 @@
       <c r="H22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" s="29" t="b">
+      <c r="I22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P22" s="28" t="b">
@@ -3318,25 +3318,25 @@
       <c r="U22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="29" t="b">
+      <c r="V22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC22" s="28" t="b">
@@ -3393,25 +3393,25 @@
       <c r="H23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="29" t="b">
+      <c r="I23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P23" s="28" t="b">
@@ -3432,25 +3432,25 @@
       <c r="U23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="29" t="b">
+      <c r="V23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC23" s="28" t="b">
@@ -3485,7 +3485,7 @@
       </c>
     </row>
     <row r="25" ht="49.5" customHeight="1">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="32" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1"/>
       <c r="J1" s="1"/>
@@ -3547,25 +3547,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -3673,122 +3673,122 @@
         <v>6.0</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL3" s="4"/>
-      <c r="AM3" s="10" t="s">
-        <v>20</v>
+      <c r="AM3" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="AN3" s="4"/>
       <c r="AO3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1.0</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="7" t="b">
+      <c r="C4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI4" s="4">
@@ -3815,7 +3815,7 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="b">
         <v>1</v>
@@ -3926,7 +3926,7 @@
         <v>미이수</v>
       </c>
       <c r="AL5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="1"/>
@@ -3937,7 +3937,7 @@
         <v>3.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="12" t="b">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7" s="12" t="b">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="21" t="b">
         <v>0</v>
@@ -4199,25 +4199,25 @@
       <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="b">
+      <c r="I8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P8" s="17" t="b">
@@ -4299,7 +4299,7 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" s="12" t="b">
         <v>0</v>
@@ -4419,7 +4419,7 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="12" t="b">
         <v>0</v>
@@ -4539,7 +4539,7 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="14" t="b">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="12" t="b">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" s="14" t="b">
         <v>0</v>
@@ -4899,106 +4899,106 @@
       <c r="AO13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>11.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="7" t="b">
+      <c r="B14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI14" s="4">
@@ -5023,7 +5023,7 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C15" s="12" t="b">
         <v>0</v>
@@ -5143,7 +5143,7 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C16" s="12" t="b">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2" t="b">
         <v>1</v>
@@ -5374,7 +5374,7 @@
         <v>미이수</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1"/>
@@ -5403,25 +5403,25 @@
       <c r="H18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="18" t="b">
+      <c r="I18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P18" s="17" t="b">
@@ -5875,25 +5875,25 @@
       <c r="H22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" s="29" t="b">
+      <c r="I22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P22" s="28" t="b">
@@ -5914,25 +5914,25 @@
       <c r="U22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="32" t="b">
+      <c r="V22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="31" t="b">
         <v>0</v>
       </c>
       <c r="AC22" s="28" t="b">
@@ -5989,25 +5989,25 @@
       <c r="H23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="29" t="b">
+      <c r="I23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P23" s="28" t="b">
@@ -6028,25 +6028,25 @@
       <c r="U23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="32" t="b">
+      <c r="V23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="31" t="b">
         <v>0</v>
       </c>
       <c r="AC23" s="28" t="b">
@@ -6081,18 +6081,18 @@
       </c>
     </row>
     <row r="25" ht="47.25" customHeight="1">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="32" t="s">
         <v>68</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P25" s="35"/>
       <c r="V25" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -6140,7 +6140,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1"/>
       <c r="J1" s="1"/>
@@ -6154,25 +6154,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -6279,119 +6279,119 @@
         <v>6.0</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="6" t="b">
+      <c r="B4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="b">
+      <c r="D4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="b">
+      <c r="E4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="F4" s="6" t="b">
+      <c r="F4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="G4" s="6" t="b">
+      <c r="G4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="6" t="b">
+      <c r="H4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="8" t="b">
+      <c r="I4" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="b">
+      <c r="J4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="Q4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6" t="b">
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="T4" s="6" t="b">
+      <c r="T4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="U4" s="6" t="b">
+      <c r="U4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="V4" s="8" t="b">
+      <c r="V4" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="W4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="8" t="b">
+      <c r="W4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="Z4" s="8" t="b">
+      <c r="Z4" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="AA4" s="8" t="b">
+      <c r="AA4" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="AB4" s="8" t="b">
+      <c r="AB4" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="AC4" s="6" t="b">
+      <c r="AC4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AD4" s="6" t="b">
+      <c r="AD4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AE4" s="6" t="b">
+      <c r="AE4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AF4" s="6" t="b">
+      <c r="AF4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AG4" s="6" t="b">
+      <c r="AG4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AH4" s="6" t="b">
+      <c r="AH4" s="8" t="b">
         <v>1</v>
       </c>
       <c r="AI4" s="4">
@@ -6415,7 +6415,7 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="12" t="b">
         <v>0</v>
@@ -6534,7 +6534,7 @@
         <v>3.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" s="12" t="b">
         <v>0</v>
@@ -6653,7 +6653,7 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C7" s="12" t="b">
         <v>0</v>
@@ -6772,7 +6772,7 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="17" t="b">
         <v>0</v>
@@ -6792,25 +6792,25 @@
       <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="b">
+      <c r="I8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P8" s="17" t="b">
@@ -6834,22 +6834,22 @@
       <c r="V8" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="W8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="18" t="b">
+      <c r="W8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC8" s="17" t="b">
@@ -6891,7 +6891,7 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C9" s="12" t="b">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12" t="b">
         <v>0</v>
@@ -7129,7 +7129,7 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="b">
         <v>1</v>
@@ -7248,7 +7248,7 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="12" t="b">
         <v>0</v>
@@ -7367,7 +7367,7 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2" t="b">
         <v>1</v>
@@ -7482,106 +7482,106 @@
       <c r="AN13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>11.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="7" t="b">
+      <c r="B14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI14" s="4">
@@ -7605,7 +7605,7 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C15" s="12" t="b">
         <v>0</v>
@@ -7724,7 +7724,7 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C16" s="12" t="b">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C17" s="12" t="b">
         <v>0</v>
@@ -7962,24 +7962,24 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="19" t="b">
+        <v>62</v>
+      </c>
+      <c r="C18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="D18" s="19" t="b">
+      <c r="D18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="19" t="b">
+      <c r="E18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="19" t="b">
+      <c r="F18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" s="19" t="b">
+      <c r="G18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H18" s="19" t="b">
+      <c r="H18" s="18" t="b">
         <v>1</v>
       </c>
       <c r="I18" s="20" t="b">
@@ -8003,22 +8003,22 @@
       <c r="O18" s="20" t="b">
         <v>1</v>
       </c>
-      <c r="P18" s="19" t="b">
+      <c r="P18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="Q18" s="19" t="b">
+      <c r="Q18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="R18" s="19" t="b">
+      <c r="R18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="S18" s="19" t="b">
+      <c r="S18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="T18" s="19" t="b">
+      <c r="T18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="U18" s="19" t="b">
+      <c r="U18" s="18" t="b">
         <v>1</v>
       </c>
       <c r="V18" s="20" t="b">
@@ -8042,22 +8042,22 @@
       <c r="AB18" s="20" t="b">
         <v>1</v>
       </c>
-      <c r="AC18" s="19" t="b">
+      <c r="AC18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="AD18" s="19" t="b">
+      <c r="AD18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="AE18" s="19" t="b">
+      <c r="AE18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="AF18" s="19" t="b">
+      <c r="AF18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="AG18" s="19" t="b">
+      <c r="AG18" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="AH18" s="19" t="b">
+      <c r="AH18" s="18" t="b">
         <v>1</v>
       </c>
       <c r="AI18" s="4">
@@ -8450,25 +8450,25 @@
       <c r="H22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" s="29" t="b">
+      <c r="I22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P22" s="28" t="b">
@@ -8489,25 +8489,25 @@
       <c r="U22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="29" t="b">
+      <c r="V22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC22" s="28" t="b">
@@ -8564,25 +8564,25 @@
       <c r="H23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="29" t="b">
+      <c r="I23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P23" s="28" t="b">
@@ -8603,25 +8603,25 @@
       <c r="U23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="29" t="b">
+      <c r="V23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC23" s="28" t="b">
@@ -8656,20 +8656,20 @@
       </c>
     </row>
     <row r="25" ht="49.5" customHeight="1">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="32" t="s">
         <v>68</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I25" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="P25" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="P25" s="33" t="s">
-        <v>77</v>
-      </c>
       <c r="V25" s="33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC25" s="33" t="s">
         <v>78</v>
@@ -8721,7 +8721,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1"/>
       <c r="J1" s="1"/>
@@ -8735,25 +8735,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -8860,119 +8860,119 @@
         <v>6.0</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="7" t="b">
+      <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI4" s="4">
@@ -8996,7 +8996,7 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="12" t="b">
         <v>0</v>
@@ -9115,7 +9115,7 @@
         <v>3.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6" s="12" t="b">
         <v>0</v>
@@ -9234,7 +9234,7 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" s="12" t="b">
         <v>0</v>
@@ -9358,7 +9358,7 @@
       <c r="C8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="D8" s="19" t="b">
+      <c r="D8" s="18" t="b">
         <v>0</v>
       </c>
       <c r="E8" s="17" t="b">
@@ -9373,28 +9373,28 @@
       <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" s="19" t="b">
+      <c r="I8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="18" t="b">
         <v>0</v>
       </c>
       <c r="Q8" s="17" t="b">
@@ -9412,25 +9412,25 @@
       <c r="U8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="18" t="b">
+      <c r="V8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC8" s="17" t="b">
@@ -9829,7 +9829,7 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="12" t="b">
         <v>0</v>
@@ -9948,7 +9948,7 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="12" t="b">
         <v>0</v>
@@ -10063,16 +10063,16 @@
       <c r="AN13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>11.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="11" t="b">
+      <c r="B14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E14" s="22" t="b">
@@ -10087,7 +10087,7 @@
       <c r="H14" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="I14" s="11" t="b">
+      <c r="I14" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J14" s="22" t="b">
@@ -10108,7 +10108,7 @@
       <c r="O14" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="P14" s="11" t="b">
+      <c r="P14" s="7" t="b">
         <v>0</v>
       </c>
       <c r="Q14" s="22" t="b">
@@ -10548,7 +10548,7 @@
       <c r="C18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="D18" s="19" t="b">
+      <c r="D18" s="18" t="b">
         <v>0</v>
       </c>
       <c r="E18" s="17" t="b">
@@ -10584,7 +10584,7 @@
       <c r="O18" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="P18" s="19" t="b">
+      <c r="P18" s="18" t="b">
         <v>0</v>
       </c>
       <c r="Q18" s="17" t="b">
@@ -10602,25 +10602,25 @@
       <c r="U18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="18" t="b">
+      <c r="V18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC18" s="17" t="b">
@@ -11024,7 +11024,7 @@
       <c r="C22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="D22" s="30" t="b">
+      <c r="D22" s="29" t="b">
         <v>0</v>
       </c>
       <c r="E22" s="28" t="b">
@@ -11039,28 +11039,28 @@
       <c r="H22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="30" t="b">
+      <c r="I22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="29" t="b">
         <v>0</v>
       </c>
       <c r="Q22" s="28" t="b">
@@ -11078,25 +11078,25 @@
       <c r="U22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="29" t="b">
+      <c r="V22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC22" s="28" t="b">
@@ -11138,7 +11138,7 @@
       <c r="C23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="D23" s="30" t="b">
+      <c r="D23" s="29" t="b">
         <v>0</v>
       </c>
       <c r="E23" s="28" t="b">
@@ -11153,28 +11153,28 @@
       <c r="H23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" s="30" t="b">
+      <c r="I23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="29" t="b">
         <v>0</v>
       </c>
       <c r="Q23" s="28" t="b">
@@ -11192,25 +11192,25 @@
       <c r="U23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="29" t="b">
+      <c r="V23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC23" s="28" t="b">
@@ -11245,7 +11245,7 @@
       </c>
     </row>
     <row r="25" ht="49.5" customHeight="1">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="32" t="s">
         <v>68</v>
       </c>
       <c r="C25" s="33" t="s">
@@ -11324,25 +11324,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -11449,119 +11449,119 @@
         <v>6.0</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1.0</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="7" t="b">
+      <c r="C4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI4" s="4">
@@ -11585,7 +11585,7 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C5" s="12" t="b">
         <v>0</v>
@@ -11704,7 +11704,7 @@
         <v>3.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C6" s="12" t="b">
         <v>0</v>
@@ -11823,7 +11823,7 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C7" s="12" t="b">
         <v>0</v>
@@ -11942,7 +11942,7 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C8" s="17" t="b">
         <v>0</v>
@@ -11962,25 +11962,25 @@
       <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="b">
+      <c r="I8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P8" s="17" t="b">
@@ -12001,25 +12001,25 @@
       <c r="U8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="18" t="b">
+      <c r="V8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC8" s="17" t="b">
@@ -12061,7 +12061,7 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C9" s="12" t="b">
         <v>0</v>
@@ -12180,7 +12180,7 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C10" s="12" t="b">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C11" s="12" t="b">
         <v>0</v>
@@ -12418,7 +12418,7 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C12" s="12" t="b">
         <v>0</v>
@@ -12537,7 +12537,7 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C13" s="12" t="b">
         <v>0</v>
@@ -12652,106 +12652,106 @@
       <c r="AN13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>11.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="6" t="b">
+      <c r="B14" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="D14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="6" t="b">
+      <c r="D14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AD14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="7" t="b">
+      <c r="AD14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI14" s="4">
@@ -12775,7 +12775,7 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C15" s="12" t="b">
         <v>0</v>
@@ -12894,7 +12894,7 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C16" s="12" t="b">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C17" s="12" t="b">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C18" s="17" t="b">
         <v>0</v>
@@ -13152,25 +13152,25 @@
       <c r="H18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="18" t="b">
+      <c r="I18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P18" s="17" t="b">
@@ -13191,25 +13191,25 @@
       <c r="U18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="18" t="b">
+      <c r="V18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC18" s="17" t="b">
@@ -13251,7 +13251,7 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C19" s="12" t="b">
         <v>0</v>
@@ -13370,7 +13370,7 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C20" s="12" t="b">
         <v>0</v>
@@ -13489,7 +13489,7 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C21" s="12" t="b">
         <v>0</v>
@@ -13626,25 +13626,25 @@
       <c r="H22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" s="29" t="b">
+      <c r="I22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P22" s="28" t="b">
@@ -13665,25 +13665,25 @@
       <c r="U22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="29" t="b">
+      <c r="V22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC22" s="28" t="b">
@@ -13740,25 +13740,25 @@
       <c r="H23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="29" t="b">
+      <c r="I23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P23" s="28" t="b">
@@ -13779,25 +13779,25 @@
       <c r="U23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="29" t="b">
+      <c r="V23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC23" s="28" t="b">
@@ -13832,17 +13832,17 @@
       </c>
     </row>
     <row r="25" ht="49.5" customHeight="1">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="32" t="s">
         <v>68</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I25" s="36"/>
       <c r="P25" s="36"/>
       <c r="V25" s="36"/>
       <c r="AC25" s="34" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -13891,7 +13891,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C1" s="1"/>
       <c r="J1" s="1"/>
@@ -13905,25 +13905,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -14030,119 +14030,119 @@
         <v>6.0</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="6" t="b">
+      <c r="B4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AD4" s="6" t="b">
+      <c r="AD4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AE4" s="6" t="b">
+      <c r="AE4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AF4" s="6" t="b">
+      <c r="AF4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AG4" s="6" t="b">
+      <c r="AG4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="AH4" s="6" t="b">
+      <c r="AH4" s="8" t="b">
         <v>1</v>
       </c>
       <c r="AI4" s="4">
@@ -14166,7 +14166,7 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" s="12" t="b">
         <v>0</v>
@@ -14404,7 +14404,7 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C7" s="12" t="b">
         <v>0</v>
@@ -14523,7 +14523,7 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C8" s="17" t="b">
         <v>0</v>
@@ -14543,25 +14543,25 @@
       <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="b">
+      <c r="I8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P8" s="17" t="b">
@@ -14585,25 +14585,25 @@
       <c r="V8" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="W8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="19" t="b">
+      <c r="W8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="18" t="b">
         <v>0</v>
       </c>
       <c r="AD8" s="17" t="b">
@@ -14642,7 +14642,7 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C9" s="12" t="b">
         <v>0</v>
@@ -14761,7 +14761,7 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C10" s="12" t="b">
         <v>0</v>
@@ -14880,7 +14880,7 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C11" s="12" t="b">
         <v>0</v>
@@ -14999,7 +14999,7 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C12" s="12" t="b">
         <v>0</v>
@@ -15118,7 +15118,7 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C13" s="12" t="b">
         <v>0</v>
@@ -15233,106 +15233,106 @@
       <c r="AN13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>11.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" s="8" t="b">
+      <c r="B14" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="W14" s="8" t="b">
+      <c r="W14" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="X14" s="8" t="b">
+      <c r="X14" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="Y14" s="8" t="b">
+      <c r="Y14" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="Z14" s="8" t="b">
+      <c r="Z14" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="AA14" s="8" t="b">
+      <c r="AA14" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="AB14" s="8" t="b">
+      <c r="AB14" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="AC14" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="7" t="b">
+      <c r="AC14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI14" s="4">
@@ -15356,7 +15356,7 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C15" s="12" t="b">
         <v>0</v>
@@ -15475,7 +15475,7 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C16" s="12" t="b">
         <v>0</v>
@@ -15729,25 +15729,25 @@
       <c r="H18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="18" t="b">
+      <c r="I18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P18" s="17" t="b">
@@ -15768,25 +15768,25 @@
       <c r="U18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="18" t="b">
+      <c r="V18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC18" s="17" t="b">
@@ -16197,25 +16197,25 @@
       <c r="H22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" s="29" t="b">
+      <c r="I22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P22" s="28" t="b">
@@ -16236,25 +16236,25 @@
       <c r="U22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="29" t="b">
+      <c r="V22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC22" s="28" t="b">
@@ -16311,25 +16311,25 @@
       <c r="H23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="29" t="b">
+      <c r="I23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P23" s="28" t="b">
@@ -16350,25 +16350,25 @@
       <c r="U23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="29" t="b">
+      <c r="V23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC23" s="28" t="b">
@@ -16403,19 +16403,19 @@
       </c>
     </row>
     <row r="25" ht="49.5" customHeight="1">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="32" t="s">
         <v>68</v>
       </c>
       <c r="C25" s="36"/>
       <c r="I25" s="36"/>
       <c r="P25" s="34" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="V25" s="34" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="AC25" s="34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -16464,7 +16464,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1"/>
       <c r="J1" s="1"/>
@@ -16478,25 +16478,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -16603,119 +16603,119 @@
         <v>6.0</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="7" t="b">
+      <c r="B4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="8" t="b">
         <v>0</v>
       </c>
       <c r="AI4" s="4">
@@ -16739,7 +16739,7 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" s="12" t="b">
         <v>0</v>
@@ -16780,16 +16780,16 @@
       <c r="O5" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" s="12" t="b">
+      <c r="P5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T5" s="12" t="b">
@@ -16798,16 +16798,16 @@
       <c r="U5" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V5" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X5" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="13" t="b">
+      <c r="V5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z5" s="13" t="b">
@@ -16819,22 +16819,22 @@
       <c r="AB5" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="12" t="b">
+      <c r="AC5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI5" s="4">
@@ -16899,16 +16899,16 @@
       <c r="O6" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" s="12" t="b">
+      <c r="P6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T6" s="12" t="b">
@@ -16917,16 +16917,16 @@
       <c r="U6" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V6" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X6" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="13" t="b">
+      <c r="V6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z6" s="13" t="b">
@@ -16938,31 +16938,31 @@
       <c r="AB6" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="12" t="b">
-        <v>0</v>
+      <c r="AC6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="AI6" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ6" s="1">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK6" s="4" t="str">
         <f t="shared" si="3"/>
@@ -16977,7 +16977,7 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="12" t="b">
         <v>0</v>
@@ -17018,16 +17018,16 @@
       <c r="O7" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" s="12" t="b">
+      <c r="P7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T7" s="12" t="b">
@@ -17036,16 +17036,16 @@
       <c r="U7" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V7" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X7" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="13" t="b">
+      <c r="V7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z7" s="13" t="b">
@@ -17057,31 +17057,31 @@
       <c r="AB7" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="12" t="b">
-        <v>0</v>
+      <c r="AC7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="AI7" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ7" s="1">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK7" s="4" t="str">
         <f t="shared" si="3"/>
@@ -17096,7 +17096,7 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="17" t="b">
         <v>0</v>
@@ -17116,37 +17116,37 @@
       <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" s="17" t="b">
+      <c r="I8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" s="18" t="b">
         <v>0</v>
       </c>
       <c r="T8" s="17" t="b">
@@ -17155,52 +17155,52 @@
       <c r="U8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="17" t="b">
-        <v>0</v>
+      <c r="V8" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="18" t="b">
+        <v>1</v>
       </c>
       <c r="AI8" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ8" s="1">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK8" s="4" t="str">
         <f t="shared" si="3"/>
@@ -17215,7 +17215,7 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="12" t="b">
         <v>0</v>
@@ -17256,16 +17256,16 @@
       <c r="O9" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9" s="12" t="b">
+      <c r="P9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T9" s="12" t="b">
@@ -17274,16 +17274,16 @@
       <c r="U9" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V9" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X9" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="13" t="b">
+      <c r="V9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z9" s="13" t="b">
@@ -17295,31 +17295,31 @@
       <c r="AB9" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="12" t="b">
+      <c r="AC9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI9" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ9" s="1">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK9" s="4" t="str">
         <f t="shared" si="3"/>
@@ -17334,7 +17334,7 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="12" t="b">
         <v>0</v>
@@ -17375,16 +17375,16 @@
       <c r="O10" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" s="12" t="b">
+      <c r="P10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T10" s="12" t="b">
@@ -17393,16 +17393,16 @@
       <c r="U10" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V10" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X10" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="13" t="b">
+      <c r="V10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z10" s="13" t="b">
@@ -17414,31 +17414,31 @@
       <c r="AB10" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="12" t="b">
+      <c r="AC10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI10" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ10" s="1">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK10" s="4" t="str">
         <f t="shared" si="3"/>
@@ -17453,7 +17453,7 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C11" s="12" t="b">
         <v>0</v>
@@ -17494,16 +17494,16 @@
       <c r="O11" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11" s="12" t="b">
+      <c r="P11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T11" s="12" t="b">
@@ -17512,16 +17512,16 @@
       <c r="U11" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V11" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W11" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X11" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="13" t="b">
+      <c r="V11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z11" s="13" t="b">
@@ -17533,22 +17533,22 @@
       <c r="AB11" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="12" t="b">
+      <c r="AC11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI11" s="4">
@@ -17572,7 +17572,7 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C12" s="12" t="b">
         <v>0</v>
@@ -17613,16 +17613,16 @@
       <c r="O12" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S12" s="12" t="b">
+      <c r="P12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T12" s="12" t="b">
@@ -17631,16 +17631,16 @@
       <c r="U12" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V12" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W12" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X12" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="13" t="b">
+      <c r="V12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z12" s="13" t="b">
@@ -17652,22 +17652,22 @@
       <c r="AB12" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="12" t="b">
+      <c r="AC12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI12" s="4">
@@ -17691,7 +17691,7 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C13" s="12" t="b">
         <v>0</v>
@@ -17732,16 +17732,16 @@
       <c r="O13" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S13" s="12" t="b">
+      <c r="P13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T13" s="12" t="b">
@@ -17750,17 +17750,17 @@
       <c r="U13" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V13" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W13" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X13" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="13" t="b">
-        <v>0</v>
+      <c r="V13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="Z13" s="13" t="b">
         <v>0</v>
@@ -17771,31 +17771,31 @@
       <c r="AB13" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="12" t="b">
+      <c r="AC13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ13" s="1">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AK13" s="4" t="str">
         <f t="shared" si="3"/>
@@ -17806,106 +17806,106 @@
       <c r="AN13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>11.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="7" t="b">
+      <c r="B14" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="8" t="b">
         <v>0</v>
       </c>
       <c r="AI14" s="4">
@@ -17929,7 +17929,7 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C15" s="12" t="b">
         <v>0</v>
@@ -17970,16 +17970,16 @@
       <c r="O15" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P15" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R15" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S15" s="12" t="b">
+      <c r="P15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T15" s="12" t="b">
@@ -17988,16 +17988,16 @@
       <c r="U15" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V15" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W15" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X15" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="13" t="b">
+      <c r="V15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z15" s="13" t="b">
@@ -18009,31 +18009,31 @@
       <c r="AB15" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC15" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="12" t="b">
-        <v>0</v>
+      <c r="AC15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK15" s="4" t="str">
         <f t="shared" si="3"/>
@@ -18048,7 +18048,7 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" s="12" t="b">
         <v>0</v>
@@ -18089,16 +18089,16 @@
       <c r="O16" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16" s="12" t="b">
+      <c r="P16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T16" s="12" t="b">
@@ -18107,16 +18107,16 @@
       <c r="U16" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V16" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W16" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="13" t="b">
+      <c r="V16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z16" s="13" t="b">
@@ -18128,22 +18128,22 @@
       <c r="AB16" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="12" t="b">
+      <c r="AC16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI16" s="4">
@@ -18208,16 +18208,16 @@
       <c r="O17" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P17" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R17" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S17" s="12" t="b">
+      <c r="P17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T17" s="12" t="b">
@@ -18226,16 +18226,16 @@
       <c r="U17" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V17" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W17" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="13" t="b">
+      <c r="V17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z17" s="13" t="b">
@@ -18247,22 +18247,22 @@
       <c r="AB17" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC17" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="12" t="b">
+      <c r="AC17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI17" s="4">
@@ -18306,37 +18306,37 @@
       <c r="H18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18" s="17" t="b">
+      <c r="I18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" s="18" t="b">
         <v>0</v>
       </c>
       <c r="T18" s="17" t="b">
@@ -18345,52 +18345,52 @@
       <c r="U18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="17" t="b">
-        <v>0</v>
+      <c r="V18" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="18" t="b">
+        <v>1</v>
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ18" s="1">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK18" s="4" t="str">
         <f t="shared" si="3"/>
@@ -18446,16 +18446,16 @@
       <c r="O19" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P19" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R19" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S19" s="12" t="b">
+      <c r="P19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T19" s="12" t="b">
@@ -18464,16 +18464,16 @@
       <c r="U19" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V19" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W19" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X19" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="13" t="b">
+      <c r="V19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z19" s="13" t="b">
@@ -18485,22 +18485,22 @@
       <c r="AB19" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC19" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="12" t="b">
+      <c r="AC19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI19" s="4">
@@ -18524,7 +18524,7 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="12" t="b">
         <v>0</v>
@@ -18565,16 +18565,16 @@
       <c r="O20" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P20" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R20" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S20" s="12" t="b">
+      <c r="P20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T20" s="12" t="b">
@@ -18583,16 +18583,16 @@
       <c r="U20" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V20" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W20" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X20" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="13" t="b">
+      <c r="V20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z20" s="13" t="b">
@@ -18604,22 +18604,22 @@
       <c r="AB20" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC20" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="12" t="b">
+      <c r="AC20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI20" s="4">
@@ -18643,7 +18643,7 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C21" s="12" t="b">
         <v>0</v>
@@ -18684,16 +18684,16 @@
       <c r="O21" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="P21" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R21" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S21" s="12" t="b">
+      <c r="P21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T21" s="12" t="b">
@@ -18702,16 +18702,16 @@
       <c r="U21" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="V21" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W21" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X21" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="13" t="b">
+      <c r="V21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3" t="b">
         <v>0</v>
       </c>
       <c r="Z21" s="13" t="b">
@@ -18723,22 +18723,22 @@
       <c r="AB21" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="AC21" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="12" t="b">
+      <c r="AC21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AI21" s="4">
@@ -18780,37 +18780,37 @@
       <c r="H22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="R22" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S22" s="28" t="b">
+      <c r="I22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29" t="b">
         <v>0</v>
       </c>
       <c r="T22" s="28" t="b">
@@ -18819,43 +18819,43 @@
       <c r="U22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="28" t="b">
+      <c r="V22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="29" t="b">
         <v>0</v>
       </c>
       <c r="AI22" s="4">
@@ -18894,37 +18894,37 @@
       <c r="H23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="R23" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S23" s="28" t="b">
+      <c r="I23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" s="29" t="b">
         <v>0</v>
       </c>
       <c r="T23" s="28" t="b">
@@ -18933,43 +18933,43 @@
       <c r="U23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="28" t="b">
+      <c r="V23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="29" t="b">
         <v>0</v>
       </c>
       <c r="AI23" s="4">
@@ -18986,8 +18986,17 @@
       </c>
     </row>
     <row r="25" ht="49.5" customHeight="1">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="32" t="s">
         <v>68</v>
+      </c>
+      <c r="P25" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="35" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19022,6 +19031,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -19035,7 +19045,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1"/>
       <c r="J1" s="1"/>
@@ -19049,25 +19059,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -19174,119 +19184,119 @@
         <v>6.0</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>1.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="7" t="b">
+      <c r="B4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI4" s="4">
@@ -19310,7 +19320,7 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C5" s="12" t="b">
         <v>0</v>
@@ -19429,7 +19439,7 @@
         <v>3.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C6" s="12" t="b">
         <v>0</v>
@@ -19548,7 +19558,7 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C7" s="12" t="b">
         <v>0</v>
@@ -19667,7 +19677,7 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C8" s="17" t="b">
         <v>0</v>
@@ -19687,25 +19697,25 @@
       <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="b">
+      <c r="I8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P8" s="17" t="b">
@@ -19726,25 +19736,25 @@
       <c r="U8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="18" t="b">
+      <c r="V8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC8" s="17" t="b">
@@ -19786,7 +19796,7 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C9" s="12" t="b">
         <v>0</v>
@@ -19905,7 +19915,7 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C10" s="12" t="b">
         <v>0</v>
@@ -20024,7 +20034,7 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C11" s="12" t="b">
         <v>0</v>
@@ -20143,7 +20153,7 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C12" s="12" t="b">
         <v>0</v>
@@ -20262,7 +20272,7 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C13" s="12" t="b">
         <v>0</v>
@@ -20377,106 +20387,106 @@
       <c r="AN13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>11.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="7" t="b">
+      <c r="B14" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AI14" s="4">
@@ -20500,7 +20510,7 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C15" s="12" t="b">
         <v>0</v>
@@ -20619,7 +20629,7 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C16" s="12" t="b">
         <v>0</v>
@@ -20738,7 +20748,7 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C17" s="12" t="b">
         <v>0</v>
@@ -20857,7 +20867,7 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="17" t="b">
         <v>0</v>
@@ -20877,25 +20887,25 @@
       <c r="H18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="18" t="b">
+      <c r="I18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="P18" s="17" t="b">
@@ -20916,25 +20926,25 @@
       <c r="U18" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="V18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="18" t="b">
+      <c r="V18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="19" t="b">
         <v>0</v>
       </c>
       <c r="AC18" s="17" t="b">
@@ -20976,7 +20986,7 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C19" s="12" t="b">
         <v>0</v>
@@ -21095,7 +21105,7 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C20" s="12" t="b">
         <v>0</v>
@@ -21214,7 +21224,7 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C21" s="12" t="b">
         <v>0</v>
@@ -21333,7 +21343,7 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C22" s="28" t="b">
         <v>0</v>
@@ -21353,25 +21363,25 @@
       <c r="H22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" s="29" t="b">
+      <c r="I22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P22" s="28" t="b">
@@ -21392,25 +21402,25 @@
       <c r="U22" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="29" t="b">
+      <c r="V22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC22" s="28" t="b">
@@ -21449,7 +21459,7 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C23" s="28" t="b">
         <v>0</v>
@@ -21469,25 +21479,25 @@
       <c r="H23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" s="29" t="b">
+      <c r="I23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="P23" s="28" t="b">
@@ -21508,25 +21518,25 @@
       <c r="U23" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="29" t="b">
+      <c r="V23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="30" t="b">
         <v>0</v>
       </c>
       <c r="AC23" s="28" t="b">
@@ -21565,11 +21575,11 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" ht="49.5" customHeight="1">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="32" t="s">
         <v>68</v>
       </c>
     </row>
@@ -21594,6 +21604,9 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
   </mergeCells>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>